--- a/基本設計/13_タスクとファイル_API基本設計書.xlsx
+++ b/基本設計/13_タスクとファイル_API基本設計書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R03e6b1f294274b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R770e87830bf04e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R4505f6f0a3b14bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="Rd3e10a6ebbf34171"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R922f567b35df4a54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R603bedbeb6314689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Rd2f31a541a5a40fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R449f9cad379645f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="R9162cbb9401a4401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb7084de687aa4f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R866c584c585b4514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rc909da4893154450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="Red0826630bb84ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R3057d3c8a239469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="Reb73e56f1eca4e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="R6d1410452e914917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="Rf9f74f14763342fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="R5dd541d9fb424d0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1297,10 +1297,7 @@
       <x:c r="F16" s="196"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1316,25 +1313,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="240" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="240"/>
-      <x:c r="D19" s="240"/>
-      <x:c r="E19" s="240"/>
-      <x:c r="F19" s="240"/>
-      <x:c r="G19" s="240"/>
-      <x:c r="H19" s="240"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="240"/>
-      <x:c r="C20" s="240"/>
-      <x:c r="D20" s="240"/>
-      <x:c r="E20" s="240"/>
-      <x:c r="F20" s="240"/>
-      <x:c r="G20" s="240"/>
-      <x:c r="H20" s="240"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="240"/>
@@ -3042,17 +3036,15 @@
       <x:c r="I19" s="64"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="88" t="str">
-        <x:v>Class名、Method名、SQLは詳細設計で定義する。ただし本SheetのURL、I/O、権限、Data範囲、Error契約はPG判断で変更しない。</x:v>
-      </x:c>
-      <x:c r="B20" s="89"/>
-      <x:c r="C20" s="89"/>
-      <x:c r="D20" s="89"/>
-      <x:c r="E20" s="89"/>
-      <x:c r="F20" s="89"/>
-      <x:c r="G20" s="89"/>
-      <x:c r="H20" s="89"/>
-      <x:c r="I20" s="90"/>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="91"/>

--- a/基本設計/13_タスクとファイル_API基本設計書.xlsx
+++ b/基本設計/13_タスクとファイル_API基本設計書.xlsx
@@ -2,15 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb7084de687aa4f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R866c584c585b4514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rc909da4893154450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="Red0826630bb84ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R3057d3c8a239469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="Reb73e56f1eca4e48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="R6d1410452e914917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="Rf9f74f14763342fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="R5dd541d9fb424d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re41d50e7a792412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd6e779fe063b4997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Reae764fee20743d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R300c036a70ff4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R4b597d0aa2bf4829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Re43f600c7bdb43e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R6ad50eaa0d934c6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -163,8 +161,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -306,8 +315,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -365,11 +384,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="241">
+  <x:cellXfs count="258">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -867,6 +900,53 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1235,8 +1315,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1245,8 +1325,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="235" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="243" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="196" t="str">
         <x:v>CW-BD-API-TSK</x:v>
@@ -1258,8 +1338,8 @@
       <x:c r="C13" s="235" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="196" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="244" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
@@ -1268,8 +1348,8 @@
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="196" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="244" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
@@ -1290,24 +1370,29 @@
       <x:c r="C16" s="235" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="196" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="244" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="196"/>
       <x:c r="F16" s="196"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="246"/>
+      <x:c r="B17" s="246"/>
+      <x:c r="C17" s="246"/>
+      <x:c r="D17" s="246"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="246"/>
+      <x:c r="B18" s="246"/>
+      <x:c r="C18" s="246" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="246" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1415,41 +1500,29 @@
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="247" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="247"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="247" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="247"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1481,7 +1554,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -1519,7 +1592,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
@@ -1545,7 +1618,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -1571,7 +1644,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
@@ -1597,7 +1670,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -1623,7 +1696,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -1648,8 +1721,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -1674,8 +1747,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -1700,25 +1773,127 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="110" customHeight="1">
+      <x:c r="A17" s="241" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B17" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C17" s="241" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D17" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" s="241" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="40" customHeight="1">
+      <x:c r="A18" s="241" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B18" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C18" s="241" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D18" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" s="241" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F18" s="241" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G18" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="241" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I18" s="241"/>
+      <x:c r="J18" s="241"/>
+      <x:c r="K18" s="241"/>
+      <x:c r="L18" s="241"/>
+    </x:row>
+    <x:row r="19" ht="100" customHeight="1">
+      <x:c r="A19" s="246" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B19" s="246" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C19" s="246" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D19" s="246" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E19" s="246" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" s="246" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="246" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H19" s="246" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1767,36 +1942,28 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-TSK-LIST</x:v>
-      </x:c>
+      <x:c r="E3" s="247" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str"/>
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="247" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="247" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
@@ -1854,7 +2021,7 @@
         <x:v>Error Code</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="39" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-TASK-001</x:v>
       </x:c>
@@ -1868,22 +2035,22 @@
         <x:v>Task検索</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-TASK-001</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>query: taskCode,title,projectId,assigneeId,reporterId,status,priority,dueFrom,dueTo,overdue,mine,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-TASK-001 Request</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>Page&lt;TaskSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-TASK-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>SCR-013, SCR-014, SCR-018</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F8／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-TASK-002</x:v>
       </x:c>
@@ -1897,22 +2064,22 @@
         <x:v>Task詳細</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-002</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-TASK-002 Request</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>TaskDetail + comments[] + attachments[] + histories[]</x:v>
+        <x:v>23_API項目定義：API-TASK-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>SCR-016, SCR-017</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F9／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-TASK-003</x:v>
       </x:c>
@@ -1926,22 +2093,22 @@
         <x:v>Task登録</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-TASK-003</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>body: projectId,title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-TASK-003 Request</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>id,taskCode,status,progress,version</x:v>
+        <x:v>23_API項目定義：API-TASK-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>SCR-015</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F10／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-TASK-004</x:v>
       </x:c>
@@ -1955,22 +2122,22 @@
         <x:v>Task更新</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-TASK-004</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>path: id; body: title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags,version</x:v>
+        <x:v>23_API項目定義：API-TASK-004 Request</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-TASK-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>SCR-016</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F11／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-TASK-005</x:v>
       </x:c>
@@ -1984,22 +2151,22 @@
         <x:v>Task状態更新</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>権限別</x:v>
+        <x:v>02／13_API権限対応：API-TASK-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>path: id; body: targetStatus,version</x:v>
+        <x:v>23_API項目定義：API-TASK-005 Request</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>previousStatus,currentStatus,progress,version</x:v>
+        <x:v>23_API項目定義：API-TASK-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>SCR-017, SCR-018</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>TASK-4001,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F12／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-TASK-006</x:v>
       </x:c>
@@ -2013,22 +2180,22 @@
         <x:v>進捗更新</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>担当者/PM/管理者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-006</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>path: id; body: progress Integer(0..100),version</x:v>
+        <x:v>23_API項目定義：API-TASK-006 Request</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>id,progress,version</x:v>
+        <x:v>23_API項目定義：API-TASK-006 Response（正本）</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>SCR-017</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F13／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-TASK-007</x:v>
       </x:c>
@@ -2042,22 +2209,22 @@
         <x:v>Comment登録</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>PJ Member</x:v>
+        <x:v>02／13_API権限対応：API-TASK-007</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>path: id; body: comment String(1..2000); header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-TASK-007 Request</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>id,comment,user,createdAt</x:v>
+        <x:v>23_API項目定義：API-TASK-007 Response（正本）</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>SCR-017</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F14／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-TASK-008</x:v>
       </x:c>
@@ -2071,22 +2238,22 @@
         <x:v>履歴検索</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-008</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>path: id; query: page,size</x:v>
+        <x:v>23_API項目定義：API-TASK-008 Request</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>Page&lt;TaskHistory&gt;</x:v>
+        <x:v>23_API項目定義：API-TASK-008 Response（正本）</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
         <x:v>SCR-017</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F15／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-TASK-009</x:v>
       </x:c>
@@ -2100,22 +2267,22 @@
         <x:v>添付登録</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-009</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
-        <x:v>multipart: file &lt;=10MB; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-TASK-009 Request</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>id,originalName,fileSize,mimeType,createdAt</x:v>
+        <x:v>23_API項目定義：API-TASK-009 Response（正本）</x:v>
       </x:c>
       <x:c r="H16" s="67" t="str">
         <x:v>SCR-015, SCR-017</x:v>
       </x:c>
       <x:c r="I16" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F16／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-TASK-010</x:v>
       </x:c>
@@ -2129,22 +2296,22 @@
         <x:v>添付取得</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-010</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>path: id,attachmentId</x:v>
+        <x:v>23_API項目定義：API-TASK-010 Request</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
-        <x:v>binary stream + Content-Disposition</x:v>
+        <x:v>23_API項目定義：API-TASK-010 Response（正本）</x:v>
       </x:c>
       <x:c r="H17" s="67" t="str">
         <x:v>SCR-017</x:v>
       </x:c>
       <x:c r="I17" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F17／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-TASK-011</x:v>
       </x:c>
@@ -2158,19 +2325,19 @@
         <x:v>添付削除</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
-        <x:v>権限者</x:v>
+        <x:v>02／13_API権限対応：API-TASK-011</x:v>
       </x:c>
       <x:c r="F18" s="67" t="str">
-        <x:v>path: id,attachmentId; query: version</x:v>
+        <x:v>23_API項目定義：API-TASK-011 Request</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-TASK-011 Response（正本）</x:v>
       </x:c>
       <x:c r="H18" s="67" t="str">
         <x:v>SCR-017</x:v>
       </x:c>
       <x:c r="I18" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
+        <x:v>22_API処理・権限!F18／21_エラーコード</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2579,461 +2746,311 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="68" t="str">
-        <x:v>API外部契約</x:v>
-      </x:c>
-      <x:c r="B1" s="68"/>
-      <x:c r="C1" s="68"/>
-      <x:c r="D1" s="68"/>
-      <x:c r="E1" s="68"/>
-      <x:c r="F1" s="68"/>
-      <x:c r="G1" s="68"/>
-      <x:c r="H1" s="68"/>
-      <x:c r="I1" s="68"/>
+      <x:c r="A1" s="251" t="str">
+        <x:v>21_エラーコード</x:v>
+      </x:c>
+      <x:c r="B1" s="250"/>
+      <x:c r="C1" s="250"/>
+      <x:c r="D1" s="250"/>
+      <x:c r="E1" s="250"/>
+      <x:c r="F1" s="250"/>
+      <x:c r="G1" s="250"/>
+      <x:c r="H1" s="250"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="68"/>
-      <x:c r="B2" s="68"/>
-      <x:c r="C2" s="68"/>
-      <x:c r="D2" s="68"/>
-      <x:c r="E2" s="68"/>
-      <x:c r="F2" s="68"/>
-      <x:c r="G2" s="68"/>
-      <x:c r="H2" s="68"/>
-      <x:c r="I2" s="68"/>
+      <x:c r="A2" s="250"/>
+      <x:c r="B2" s="250"/>
+      <x:c r="C2" s="250"/>
+      <x:c r="D2" s="250"/>
+      <x:c r="E2" s="250"/>
+      <x:c r="F2" s="250"/>
+      <x:c r="G2" s="250"/>
+      <x:c r="H2" s="250"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="62" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="63" t="str">
+      <x:c r="A3" s="250" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-TSK-CONTRACT</x:v>
-      </x:c>
-      <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
+      <x:c r="B3" s="250"/>
+      <x:c r="C3" s="250"/>
+      <x:c r="D3" s="250"/>
+      <x:c r="E3" s="250"/>
+      <x:c r="F3" s="250"/>
+      <x:c r="G3" s="250"/>
+      <x:c r="H3" s="250"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
-      <x:c r="I4" s="63"/>
+      <x:c r="A4" s="250"/>
+      <x:c r="B4" s="250"/>
+      <x:c r="C4" s="250"/>
+      <x:c r="D4" s="250"/>
+      <x:c r="E4" s="250"/>
+      <x:c r="F4" s="250"/>
+      <x:c r="G4" s="250"/>
+      <x:c r="H4" s="250"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="64"/>
-      <x:c r="B5" s="64"/>
-      <x:c r="C5" s="64"/>
-      <x:c r="D5" s="64"/>
-      <x:c r="E5" s="64"/>
-      <x:c r="F5" s="64"/>
-      <x:c r="G5" s="64"/>
-      <x:c r="H5" s="64"/>
-      <x:c r="I5" s="64"/>
+      <x:c r="A5" s="250" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="250"/>
+      <x:c r="C5" s="250"/>
+      <x:c r="D5" s="250"/>
+      <x:c r="E5" s="250"/>
+      <x:c r="F5" s="250"/>
+      <x:c r="G5" s="250"/>
+      <x:c r="H5" s="250"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="65" t="str">
-        <x:v>1. Task・File Request/Response・権限契約</x:v>
-      </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="66" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="str">
-        <x:v>Request定義</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="str">
-        <x:v>Response定義</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Role</x:v>
-      </x:c>
-      <x:c r="E7" s="66" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="66" t="str">
-        <x:v>参照・更新Table</x:v>
-      </x:c>
-      <x:c r="G7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="H7" s="66" t="str">
+      <x:c r="A6" s="250"/>
+      <x:c r="B6" s="250"/>
+      <x:c r="C6" s="250"/>
+      <x:c r="D6" s="250"/>
+      <x:c r="E6" s="250"/>
+      <x:c r="F6" s="250"/>
+      <x:c r="G6" s="250"/>
+      <x:c r="H6" s="250"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="253" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-      <x:c r="I7" s="66" t="str">
-        <x:v>利用画面</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="str">
-        <x:v>API-TASK-001</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>query: taskCode,title,projectId,assigneeId,reporterId,status,priority,dueFrom,dueTo,overdue,mine,page,size,sort</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>Page&lt;TaskSummary&gt;</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=参加PJ・本人Task</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>tasks,projects,project_members,employees</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I8" s="67" t="str">
-        <x:v>SCR-013, SCR-014, SCR-018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="str">
-        <x:v>API-TASK-002</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>TaskDetail + comments[] + attachments[] + histories[]</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
-        <x:v>tasks,task_tags,task_comments,task_attachments,task_histories</x:v>
-      </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I9" s="67" t="str">
-        <x:v>SCR-016, SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="str">
-        <x:v>API-TASK-003</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>body: projectId,title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>id,taskCode,status,progress,version</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
-        <x:v>tasks,task_tags,project_members,task_histories,notifications</x:v>
-      </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>TX-020</x:v>
-      </x:c>
-      <x:c r="H10" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I10" s="67" t="str">
-        <x:v>SCR-015</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="str">
-        <x:v>API-TASK-004</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>path: id; body: title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags,version</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>id,version</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
-        <x:v>tasks,task_tags,task_histories,notifications</x:v>
-      </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>TX-021</x:v>
-      </x:c>
-      <x:c r="H11" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I11" s="67" t="str">
-        <x:v>SCR-016</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="str">
-        <x:v>API-TASK-005</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>path: id; body: targetStatus,version</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>previousStatus,currentStatus,progress,version</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>権限別</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>担当者=TODO/進行/REVIEW; PM/ADMIN=承認・差戻し・取消</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>tasks,task_histories,notifications,projects</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>TX-004</x:v>
-      </x:c>
-      <x:c r="H12" s="67" t="str">
-        <x:v>TASK-4001,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I12" s="67" t="str">
-        <x:v>SCR-017, SCR-018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>API-TASK-006</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>path: id; body: progress Integer(0..100),version</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>id,progress,version</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>担当者/PM/管理者</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>担当者または担当PM/ADMIN</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>tasks,task_histories</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>TX-021</x:v>
-      </x:c>
-      <x:c r="H13" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I13" s="67" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-TASK-007</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>path: id; body: comment String(1..2000); header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>id,comment,user,createdAt</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>PJ Member</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>当該PJ Member</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>task_comments,tasks</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>TX-022</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040</x:v>
-      </x:c>
-      <x:c r="I14" s="67" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="str">
-        <x:v>API-TASK-008</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>path: id; query: page,size</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>Page&lt;TaskHistory&gt;</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>task_histories,tasks,users</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I15" s="67" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="67" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B16" s="67" t="str">
-        <x:v>multipart: file &lt;=10MB; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>id,originalName,fileSize,mimeType,createdAt</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
-      </x:c>
-      <x:c r="F16" s="67" t="str">
-        <x:v>task_attachments,tasks,operation_logs</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>TX-007</x:v>
-      </x:c>
-      <x:c r="H16" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>SCR-015, SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="67" t="str">
-        <x:v>API-TASK-010</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="str">
-        <x:v>path: id,attachmentId</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="str">
-        <x:v>binary stream + Content-Disposition</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E17" s="67" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
-      </x:c>
-      <x:c r="F17" s="67" t="str">
-        <x:v>task_attachments,tasks</x:v>
-      </x:c>
-      <x:c r="G17" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H17" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I17" s="67" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="67" t="str">
-        <x:v>API-TASK-011</x:v>
-      </x:c>
-      <x:c r="B18" s="67" t="str">
-        <x:v>path: id,attachmentId; query: version</x:v>
-      </x:c>
-      <x:c r="C18" s="67" t="str">
-        <x:v>204 No Content</x:v>
-      </x:c>
-      <x:c r="D18" s="67" t="str">
-        <x:v>権限者</x:v>
-      </x:c>
-      <x:c r="E18" s="67" t="str">
-        <x:v>ADMIN/担当PM/Upload者</x:v>
-      </x:c>
-      <x:c r="F18" s="67" t="str">
-        <x:v>task_attachments,operation_logs + physical file</x:v>
-      </x:c>
-      <x:c r="G18" s="67" t="str">
-        <x:v>TX-009</x:v>
-      </x:c>
-      <x:c r="H18" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I18" s="67" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
+      <x:c r="B7" s="253" t="str">
+        <x:v>分類</x:v>
+      </x:c>
+      <x:c r="C7" s="253" t="str">
+        <x:v>業務上の意味</x:v>
+      </x:c>
+      <x:c r="D7" s="253" t="str">
+        <x:v>HTTP Status</x:v>
+      </x:c>
+      <x:c r="E7" s="253" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="F7" s="253" t="str">
+        <x:v>Log Level</x:v>
+      </x:c>
+      <x:c r="G7" s="253" t="str">
+        <x:v>再試行</x:v>
+      </x:c>
+      <x:c r="H7" s="253" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="255" t="str">
+        <x:v>TASK-4001</x:v>
+      </x:c>
+      <x:c r="B8" s="255" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C8" s="255" t="str">
+        <x:v>状態遷移不正</x:v>
+      </x:c>
+      <x:c r="D8" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E8" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F8" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G8" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H8" s="255" t="str"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="254" t="str">
+        <x:v>TASK-4002</x:v>
+      </x:c>
+      <x:c r="B9" s="254" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C9" s="254" t="str">
+        <x:v>担当者はMemberでない</x:v>
+      </x:c>
+      <x:c r="D9" s="254" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E9" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F9" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G9" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H9" s="254" t="str"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="255" t="str">
+        <x:v>TASK-4003</x:v>
+      </x:c>
+      <x:c r="B10" s="255" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C10" s="255" t="str">
+        <x:v>日付不正</x:v>
+      </x:c>
+      <x:c r="D10" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E10" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F10" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G10" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H10" s="255" t="str"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="254" t="str">
+        <x:v>TASK-4004</x:v>
+      </x:c>
+      <x:c r="B11" s="254" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C11" s="254" t="str">
+        <x:v>既に完了</x:v>
+      </x:c>
+      <x:c r="D11" s="254" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E11" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F11" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G11" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H11" s="254" t="str"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="255" t="str">
+        <x:v>FILE-4001</x:v>
+      </x:c>
+      <x:c r="B12" s="255" t="str">
+        <x:v>File</x:v>
+      </x:c>
+      <x:c r="C12" s="255" t="str">
+        <x:v>種類不許可</x:v>
+      </x:c>
+      <x:c r="D12" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E12" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F12" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G12" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H12" s="255" t="str"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="254" t="str">
+        <x:v>FILE-4002</x:v>
+      </x:c>
+      <x:c r="B13" s="254" t="str">
+        <x:v>File</x:v>
+      </x:c>
+      <x:c r="C13" s="254" t="str">
+        <x:v>Size超過</x:v>
+      </x:c>
+      <x:c r="D13" s="254" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="E13" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F13" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G13" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H13" s="254" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="64"/>
-      <x:c r="B19" s="64"/>
-      <x:c r="C19" s="64"/>
-      <x:c r="D19" s="64"/>
-      <x:c r="E19" s="64"/>
-      <x:c r="F19" s="64"/>
-      <x:c r="G19" s="64"/>
-      <x:c r="H19" s="64"/>
-      <x:c r="I19" s="64"/>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
@@ -3044,18 +3061,16 @@
       <x:c r="F20"/>
       <x:c r="G20"/>
       <x:c r="H20"/>
-      <x:c r="I20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="91"/>
-      <x:c r="B21" s="92"/>
-      <x:c r="C21" s="92"/>
-      <x:c r="D21" s="92"/>
-      <x:c r="E21" s="92"/>
-      <x:c r="F21" s="92"/>
-      <x:c r="G21" s="92"/>
-      <x:c r="H21" s="92"/>
-      <x:c r="I21" s="93"/>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
@@ -3066,7 +3081,6 @@
       <x:c r="F22"/>
       <x:c r="G22"/>
       <x:c r="H22"/>
-      <x:c r="I22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
@@ -3077,7 +3091,6 @@
       <x:c r="F23"/>
       <x:c r="G23"/>
       <x:c r="H23"/>
-      <x:c r="I23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
@@ -3088,7 +3101,6 @@
       <x:c r="F24"/>
       <x:c r="G24"/>
       <x:c r="H24"/>
-      <x:c r="I24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
@@ -3099,7 +3111,6 @@
       <x:c r="F25"/>
       <x:c r="G25"/>
       <x:c r="H25"/>
-      <x:c r="I25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
@@ -3110,7 +3121,6 @@
       <x:c r="F26"/>
       <x:c r="G26"/>
       <x:c r="H26"/>
-      <x:c r="I26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
@@ -3121,7 +3131,6 @@
       <x:c r="F27"/>
       <x:c r="G27"/>
       <x:c r="H27"/>
-      <x:c r="I27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -3132,21 +3141,102 @@
       <x:c r="F28"/>
       <x:c r="G28"/>
       <x:c r="H28"/>
-      <x:c r="I28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:I3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:I4"/>
-    <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A20:I21"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3157,593 +3247,14 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>業務エラーコード</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-053</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. Error Code</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>分類</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>HTTP Status</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>画面Message</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>記録Level</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>再試行</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>COMMON-0000</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>成功</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Request parameter error</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Data</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Data存在しない</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>COMMON-4090</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>競合</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>並行更新Conflict</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>System</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>System error</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="H12" s="33"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>TASK-4001</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>Task</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>状態遷移不正</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H13" s="33"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>TASK-4002</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>Task</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>担当者はMemberでない</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H14" s="33"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>TASK-4003</x:v>
-      </x:c>
-      <x:c r="B15" s="33" t="str">
-        <x:v>Task</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>日付不正</x:v>
-      </x:c>
-      <x:c r="D15" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E15" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G15" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H15" s="33"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>TASK-4004</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>Task</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>既に完了</x:v>
-      </x:c>
-      <x:c r="D16" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E16" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F16" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G16" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H16" s="33"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>FILE-4001</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>File</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>種類不許可</x:v>
-      </x:c>
-      <x:c r="D17" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F17" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G17" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H17" s="33"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>FILE-4002</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="str">
-        <x:v>File</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>Size超過</x:v>
-      </x:c>
-      <x:c r="D18" s="33" t="n">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="E18" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F18" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G18" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H18" s="33"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34"/>
-      <x:c r="C34"/>
-      <x:c r="D34"/>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
-      <x:c r="G34"/>
-      <x:c r="H34"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36"/>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36"/>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3774,8 +3285,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="247" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="63" t="str">
         <x:v>CW-BD-API-TSK-FLOW</x:v>
@@ -3788,14 +3299,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -3830,8 +3341,8 @@
       <x:c r="C7" s="66" t="str">
         <x:v>処理概要</x:v>
       </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Data範囲</x:v>
+      <x:c r="D7" s="256" t="str">
+        <x:v>認可参照</x:v>
       </x:c>
       <x:c r="E7" s="66" t="str">
         <x:v>Transaction</x:v>
@@ -3841,6 +3352,12 @@
       </x:c>
       <x:c r="G7" s="66" t="str">
         <x:v>Log</x:v>
+      </x:c>
+      <x:c r="H7" s="203" t="str">
+        <x:v>関連Table</x:v>
+      </x:c>
+      <x:c r="I7" s="203" t="str">
+        <x:v>利用元・補足</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -3851,10 +3368,12 @@
         <x:v>Task検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: taskCode,title,projectId,assigneeId,reporterId,status,priority,dueFrom,dueTo,overdue,mine,page,size,sortを型・必須・桁・業務Ruleで検証。3) tasks,projects,project_members,employeesを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;TaskSummary&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) tasks,projects,project_members,employeesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=参加PJ・本人Task</x:v>
+        <x:v>02／13_API権限対応 API-TASK-001
+Permission: PERM-TASK-READ
+Data Scope: DS-TASK-001</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>参照</x:v>
@@ -3864,6 +3383,12 @@
       </x:c>
       <x:c r="G8" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H8" s="203" t="str">
+        <x:v>tasks,projects,project_members,employees</x:v>
+      </x:c>
+      <x:c r="I8" s="203" t="str">
+        <x:v>SCR-013, SCR-014, SCR-018</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -3874,10 +3399,12 @@
         <x:v>Task詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) tasks,task_tags,comments,attachments,historiesを参照/更新。4) 参照の境界でCommit/Rollback。5) TaskDetail + comments[] + attachments[] + histories[]を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) tasks,task_tags,task_comments,task_attachments,task_historiesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>02／13_API権限対応 API-TASK-002
+Permission: PERM-TASK-READ
+Data Scope: DS-TASK-002</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>参照</x:v>
@@ -3888,8 +3415,14 @@
       <x:c r="G9" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="H9" s="203" t="str">
+        <x:v>tasks,task_comments,task_attachments,task_histories</x:v>
+      </x:c>
+      <x:c r="I9" s="203" t="str">
+        <x:v>SCR-016, SCR-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="264" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-TASK-003</x:v>
       </x:c>
@@ -3897,22 +3430,35 @@
         <x:v>Task登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: projectId,title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) tasks,task_tags,project_members,task_histories,notificationsを参照/更新。4) TX-TASK-CREATEの境界でCommit/Rollback。5) id,taskCode,status,progress,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) tasks,task_tags,project_members,task_histories,notificationsを参照/更新。4) TX-020の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+処理前に16／28 BR-TASK-001のPJ状態別操作可否を確認。日付更新はBR-TASK-002、担当変更は在籍ACTIVE Member必須。</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>02／13_API権限対応 API-TASK-003
+Permission: PERM-TASK-WRITE
+Data Scope: DS-TASK-003</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>TX-020</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
+        <x:v>TASK-4002, TASK-4003,COMMON-4090
+TASK-4001</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="H10" s="241" t="str">
+        <x:v>tasks,task_tags,project_members,task_histories,notifications</x:v>
+      </x:c>
+      <x:c r="I10" s="241" t="str">
+        <x:v>SCR-015</x:v>
+      </x:c>
+      <x:c r="J10" s="241"/>
+      <x:c r="K10" s="241"/>
+      <x:c r="L10" s="241"/>
+    </x:row>
+    <x:row r="11" ht="222" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-TASK-004</x:v>
       </x:c>
@@ -3920,22 +3466,35 @@
         <x:v>Task更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: title,description,assigneeId,priority,startDate,dueDate,estimatedHours,parentTaskId,tags,versionを型・必須・桁・業務Ruleで検証。3) tasks,task_tags,task_histories,notificationsを参照/更新。4) TX-TASK-UPDATEの境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) tasks,task_tags,task_histories,notificationsを参照/更新。4) TX-021の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+処理前に16／28 BR-TASK-001のPJ状態別操作可否を確認。日付更新はBR-TASK-002、担当変更は在籍ACTIVE Member必須。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>02／13_API権限対応 API-TASK-004
+Permission: PERM-TASK-WRITE
+Data Scope: DS-TASK-004</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>TX-021</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
+        <x:v>TASK-4002, TASK-4003,COMMON-4090
+TASK-4001</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="H11" s="241" t="str">
+        <x:v>tasks,task_tags,task_histories,notifications</x:v>
+      </x:c>
+      <x:c r="I11" s="241" t="str">
+        <x:v>SCR-016</x:v>
+      </x:c>
+      <x:c r="J11" s="241"/>
+      <x:c r="K11" s="241"/>
+      <x:c r="L11" s="241"/>
+    </x:row>
+    <x:row r="12" ht="110" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-TASK-005</x:v>
       </x:c>
@@ -3943,22 +3502,33 @@
         <x:v>Task状態更新</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: targetStatus,versionを型・必須・桁・業務Ruleで検証。3) tasks,task_histories,notifications,projectsを参照/更新。4) TX-004の境界でCommit/Rollback。5) previousStatus,currentStatus,progress,versionを共通Response形式で返却。</x:v>
+        <x:v>Permission/担当者・PM・ADMIN/存在/versionを確認。16／27 Task遷移およびBR-TASK-001のPJ操作境界を満たす場合だけ更新。BR-TASK-003の確定進捗、履歴、通知、PJ進捗をTX-004で一括Commit。通常REVIEW取消は不可。失敗全状態保持。</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>担当者=TODO/進行/REVIEW; PM/ADMIN=承認・差戻し・取消</x:v>
+        <x:v>02／13_API権限対応 API-TASK-005
+Permission: PERM-TASK-WRITE / PERM-TASK-PROGRESS / PERM-TASK-APPROVE
+Data Scope: DS-TASK-005</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>TX-004</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>TASK-4001,COMMON-4090</x:v>
+        <x:v>TASK-4001, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="H12" s="241" t="str">
+        <x:v>tasks,task_histories,notifications,projects</x:v>
+      </x:c>
+      <x:c r="I12" s="241" t="str">
+        <x:v>SCR-017, SCR-018</x:v>
+      </x:c>
+      <x:c r="J12" s="241"/>
+      <x:c r="K12" s="241"/>
+      <x:c r="L12" s="241"/>
+    </x:row>
+    <x:row r="13" ht="110" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-TASK-006</x:v>
       </x:c>
@@ -3966,22 +3536,33 @@
         <x:v>進捗更新</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: progress Integer(0..100),versionを型・必須・桁・業務Ruleで検証。3) tasks,task_historiesを参照/更新。4) TX-TASK-PROGRESSの境界でCommit/Rollback。5) id,progress,versionを共通Response形式で返却。</x:v>
+        <x:v>Permission/対象範囲・存在/version確認。PJ=IN_PROGRESSかつTask=IN_PROGRESSのみ。progressは整数1～99。範囲外COMMON-4000、状態不正TASK-4001。TX-021で進捗/履歴/PJ進捗・監査を更新し状態は変更しない。失敗全Rollback。</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>担当者または担当PM/ADMIN</x:v>
+        <x:v>02／13_API権限対応 API-TASK-006
+Permission: PERM-TASK-PROGRESS
+Data Scope: DS-TASK-006</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>TX-021</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
+        <x:v>COMMON-4000, TASK-4001, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="H13" s="241" t="str">
+        <x:v>tasks,task_histories</x:v>
+      </x:c>
+      <x:c r="I13" s="241" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="J13" s="241"/>
+      <x:c r="K13" s="241"/>
+      <x:c r="L13" s="241"/>
+    </x:row>
+    <x:row r="14" ht="194" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-TASK-007</x:v>
       </x:c>
@@ -3989,20 +3570,33 @@
         <x:v>Comment登録</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: comment String(1..2000); header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) task_comments,tasksを参照/更新。4) TX-COMMENTの境界でCommit/Rollback。5) id,comment,user,createdAtを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) task_comments,tasksを参照/更新。4) TX-022の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+処理前に16／28 BR-TASK-001のPJ状態別操作可否を確認。日付更新はBR-TASK-002、担当変更は在籍ACTIVE Member必須。</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>当該PJ Member</x:v>
+        <x:v>02／13_API権限対応 API-TASK-007
+Permission: PERM-TASK-READ
+Data Scope: DS-TASK-007</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>TX-022</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040</x:v>
+        <x:v>COMMON-4000, COMMON-4040
+TASK-4001</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H14" s="241" t="str">
+        <x:v>task_comments,tasks</x:v>
+      </x:c>
+      <x:c r="I14" s="241" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="J14" s="241"/>
+      <x:c r="K14" s="241"/>
+      <x:c r="L14" s="241"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="67" t="str">
@@ -4012,10 +3606,12 @@
         <x:v>履歴検索</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; query: page,sizeを型・必須・桁・業務Ruleで検証。3) task_histories,tasks,usersを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;TaskHistory&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) task_histories,tasks,usersを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>02／13_API権限対応 API-TASK-008
+Permission: PERM-TASK-READ
+Data Scope: DS-TASK-008</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>参照</x:v>
@@ -4026,8 +3622,14 @@
       <x:c r="G15" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="H15" s="203" t="str">
+        <x:v>task_histories,tasks,users</x:v>
+      </x:c>
+      <x:c r="I15" s="203" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="208" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-TASK-009</x:v>
       </x:c>
@@ -4035,20 +3637,33 @@
         <x:v>添付登録</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) multipart: file &lt;=10MB; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) task_attachments,tasks,operation_logsを参照/更新。4) TX-007の境界でCommit/Rollback。5) id,originalName,fileSize,mimeType,createdAtを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) multipart: file &lt;=10MB; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) task_attachments,tasks,operation_logsを参照/更新。4) TX-007の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+処理前に16／28 BR-TASK-001のPJ状態別操作可否を確認。日付更新はBR-TASK-002、担当変更は在籍ACTIVE Member必須。</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
+        <x:v>02／13_API権限対応 API-TASK-009
+Permission: PERM-FILE-WRITE
+Data Scope: DS-TASK-009</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>TX-007</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,COMMON-4090</x:v>
+        <x:v>FILE-4001, FILE-4002,COMMON-4090
+TASK-4001</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H16" s="241" t="str">
+        <x:v>task_attachments,tasks,operation_logs</x:v>
+      </x:c>
+      <x:c r="I16" s="241" t="str">
+        <x:v>SCR-015, SCR-017</x:v>
+      </x:c>
+      <x:c r="J16" s="241"/>
+      <x:c r="K16" s="241"/>
+      <x:c r="L16" s="241"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="67" t="str">
@@ -4058,10 +3673,12 @@
         <x:v>添付取得</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id,attachmentIdを型・必須・桁・業務Ruleで検証。3) task_attachments,tasksを参照/更新。4) 参照の境界でCommit/Rollback。5) binary stream + Content-Dispositionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) task_attachments,tasksを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
+        <x:v>02／13_API権限対応 API-TASK-010
+Permission: PERM-TASK-READ
+Data Scope: DS-TASK-010</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>参照</x:v>
@@ -4072,8 +3689,14 @@
       <x:c r="G17" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="H17" s="203" t="str">
+        <x:v>task_attachments,tasks</x:v>
+      </x:c>
+      <x:c r="I17" s="203" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="180" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-TASK-011</x:v>
       </x:c>
@@ -4081,20 +3704,33 @@
         <x:v>添付削除</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id,attachmentId; query: versionを型・必須・桁・業務Ruleで検証。3) task_attachments,operation_logs + physical fileを参照/更新。4) TX-FILE-DELETEの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) task_attachments,operation_logs + physical fileを参照/更新。4) TX-009の境界でCommit/Rollback。5) HTTP 204、Response Bodyなしで返却。
+処理前に16／28 BR-TASK-001のPJ状態別操作可否を確認。日付更新はBR-TASK-002、担当変更は在籍ACTIVE Member必須。</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
-        <x:v>ADMIN/担当PM/Upload者</x:v>
+        <x:v>02／13_API権限対応 API-TASK-011
+Permission: PERM-FILE-WRITE
+Data Scope: DS-TASK-011</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
         <x:v>TX-009</x:v>
       </x:c>
       <x:c r="F18" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
+        <x:v>COMMON-4040, COMMON-4090
+TASK-4001</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H18" s="241" t="str">
+        <x:v>task_attachments,operation_logs + physical file</x:v>
+      </x:c>
+      <x:c r="I18" s="241" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="J18" s="241"/>
+      <x:c r="K18" s="241"/>
+      <x:c r="L18" s="241"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4105,7 +3741,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4160,8 +3796,8 @@
       <x:c r="C3" s="139"/>
       <x:c r="D3" s="139"/>
       <x:c r="E3" s="139"/>
-      <x:c r="F3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="247" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="139" t="str">
         <x:v>CW-BD-13-FIELD</x:v>
@@ -4175,8 +3811,8 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -4184,8 +3820,8 @@
       <x:c r="F4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -4417,7 +4053,7 @@
         <x:v>tasks.reporter_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="24" hidden="0" customHeight="1">
+    <x:row r="13" ht="52" hidden="0" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-TASK-001</x:v>
       </x:c>
@@ -4431,28 +4067,28 @@
         <x:v>request.query.status</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Array&lt;String&gt;</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>最大5件、重複不可</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>TODO/IN_PROGRESS/REVIEW/COMPLETED/CANCELLED</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>省略可。要素Null/空文字不可</x:v>
       </x:c>
       <x:c r="J13" s="67" t="str">
-        <x:v>状態</x:v>
+        <x:v>同一Query名を繰返して送信。同項目内OR、異なる項目間AND。省略/空配列は絞込なし。Enum外=COMMON-4000。</x:v>
       </x:c>
       <x:c r="K13" s="67" t="str">
         <x:v>tasks.status</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
+    <x:row r="14" ht="52" hidden="0" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-TASK-001</x:v>
       </x:c>
@@ -4466,22 +4102,22 @@
         <x:v>request.query.priority</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Array&lt;String&gt;</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>最大4件、重複不可</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>LOW/MEDIUM/HIGH/URGENT</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>省略可。要素Null/空文字不可</x:v>
       </x:c>
       <x:c r="J14" s="67" t="str">
-        <x:v>優先度</x:v>
+        <x:v>同一Query名を繰返して送信。同項目内OR、異なる項目間AND。省略/空配列は絞込なし。Enum外=COMMON-4000。</x:v>
       </x:c>
       <x:c r="K14" s="67" t="str">
         <x:v>tasks.priority</x:v>
@@ -5067,7 +4703,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G31" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H31" s="67" t="str">
         <x:v>-</x:v>
@@ -5907,7 +5543,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G55" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H55" s="67" t="str">
         <x:v>-</x:v>
@@ -6222,7 +5858,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G64" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大5000</x:v>
       </x:c>
       <x:c r="H64" s="67" t="str">
         <x:v>-</x:v>
@@ -6957,7 +6593,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G85" s="67" t="str">
-        <x:v>最大50</x:v>
+        <x:v>最大100</x:v>
       </x:c>
       <x:c r="H85" s="67" t="str">
         <x:v>-</x:v>
@@ -7199,16 +6835,16 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F92" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G92" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大5000</x:v>
       </x:c>
       <x:c r="H92" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I92" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J92" s="67" t="str">
         <x:v>説明</x:v>
@@ -7234,7 +6870,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F93" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G93" s="67" t="str">
         <x:v>-</x:v>
@@ -7243,7 +6879,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I93" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J93" s="67" t="str">
         <x:v>担当者ID</x:v>
@@ -7287,7 +6923,7 @@
         <x:v>tasks.priority</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="15" hidden="0" customHeight="1">
+    <x:row r="95" ht="40" hidden="0" customHeight="1">
       <x:c r="A95" s="67" t="str">
         <x:v>API-TASK-003</x:v>
       </x:c>
@@ -7304,7 +6940,7 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="F95" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G95" s="67" t="str">
         <x:v>-</x:v>
@@ -7313,16 +6949,17 @@
         <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I95" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J95" s="67" t="str">
-        <x:v>開始日</x:v>
+        <x:v>任意・Null可。指定日はPJ期間内、両方指定時開始≦期限。期限Nullは通知対象外。</x:v>
       </x:c>
       <x:c r="K95" s="67" t="str">
         <x:v>tasks.start_date</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+      <x:c r="L95" s="241"/>
+    </x:row>
+    <x:row r="96" ht="40" hidden="0" customHeight="1">
       <x:c r="A96" s="67" t="str">
         <x:v>API-TASK-003</x:v>
       </x:c>
@@ -7339,7 +6976,7 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="F96" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G96" s="67" t="str">
         <x:v>-</x:v>
@@ -7348,14 +6985,15 @@
         <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I96" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J96" s="67" t="str">
-        <x:v>期限</x:v>
+        <x:v>任意・Null可。指定日はPJ期間内、両方指定時開始≦期限。期限Nullは通知対象外。</x:v>
       </x:c>
       <x:c r="K96" s="67" t="str">
         <x:v>tasks.due_date</x:v>
       </x:c>
+      <x:c r="L96" s="241"/>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="67" t="str">
@@ -7374,7 +7012,7 @@
         <x:v>Decimal</x:v>
       </x:c>
       <x:c r="F97" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G97" s="67" t="str">
         <x:v>-</x:v>
@@ -7383,7 +7021,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I97" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J97" s="67" t="str">
         <x:v>見積工数</x:v>
@@ -7409,7 +7047,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F98" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G98" s="67" t="str">
         <x:v>-</x:v>
@@ -7418,7 +7056,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I98" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J98" s="67" t="str">
         <x:v>親Task ID</x:v>
@@ -7444,19 +7082,19 @@
         <x:v>Array&lt;String&gt;</x:v>
       </x:c>
       <x:c r="F99" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G99" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大20件・各最大50</x:v>
       </x:c>
       <x:c r="H99" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I99" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J99" s="67" t="str">
-        <x:v>Tag一覧</x:v>
+        <x:v>Tag一覧（前後空白除去、空文字・重複除外）</x:v>
       </x:c>
       <x:c r="K99" s="67" t="str">
         <x:v>COLLECTION INPUT: tags[] → task_tags.tag for created task</x:v>
@@ -7934,16 +7572,16 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F113" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G113" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大5000</x:v>
       </x:c>
       <x:c r="H113" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I113" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J113" s="67" t="str">
         <x:v>説明</x:v>
@@ -7969,7 +7607,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F114" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G114" s="67" t="str">
         <x:v>-</x:v>
@@ -7978,7 +7616,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I114" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J114" s="67" t="str">
         <x:v>担当者ID</x:v>
@@ -8022,7 +7660,7 @@
         <x:v>tasks.priority</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="15" hidden="0" customHeight="1">
+    <x:row r="116" ht="40" hidden="0" customHeight="1">
       <x:c r="A116" s="67" t="str">
         <x:v>API-TASK-004</x:v>
       </x:c>
@@ -8039,7 +7677,7 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="F116" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G116" s="67" t="str">
         <x:v>-</x:v>
@@ -8048,16 +7686,17 @@
         <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I116" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J116" s="67" t="str">
-        <x:v>開始日</x:v>
+        <x:v>任意・Null可。指定日はPJ期間内、両方指定時開始≦期限。期限Nullは通知対象外。</x:v>
       </x:c>
       <x:c r="K116" s="67" t="str">
         <x:v>tasks.start_date</x:v>
       </x:c>
-    </x:row>
-    <x:row r="117" ht="15" hidden="0" customHeight="1">
+      <x:c r="L116" s="241"/>
+    </x:row>
+    <x:row r="117" ht="40" hidden="0" customHeight="1">
       <x:c r="A117" s="67" t="str">
         <x:v>API-TASK-004</x:v>
       </x:c>
@@ -8074,7 +7713,7 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="F117" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G117" s="67" t="str">
         <x:v>-</x:v>
@@ -8083,14 +7722,15 @@
         <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I117" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J117" s="67" t="str">
-        <x:v>期限</x:v>
+        <x:v>任意・Null可。指定日はPJ期間内、両方指定時開始≦期限。期限Nullは通知対象外。</x:v>
       </x:c>
       <x:c r="K117" s="67" t="str">
         <x:v>tasks.due_date</x:v>
       </x:c>
+      <x:c r="L117" s="241"/>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="67" t="str">
@@ -8109,7 +7749,7 @@
         <x:v>Decimal</x:v>
       </x:c>
       <x:c r="F118" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G118" s="67" t="str">
         <x:v>-</x:v>
@@ -8118,7 +7758,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I118" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J118" s="67" t="str">
         <x:v>見積工数</x:v>
@@ -8144,7 +7784,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F119" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G119" s="67" t="str">
         <x:v>-</x:v>
@@ -8153,7 +7793,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I119" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J119" s="67" t="str">
         <x:v>親Task ID</x:v>
@@ -8179,19 +7819,19 @@
         <x:v>Array&lt;String&gt;</x:v>
       </x:c>
       <x:c r="F120" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G120" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大20件・各最大50</x:v>
       </x:c>
       <x:c r="H120" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I120" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J120" s="67" t="str">
-        <x:v>Tag一覧</x:v>
+        <x:v>Tag一覧（前後空白除去、空文字・重複除外）</x:v>
       </x:c>
       <x:c r="K120" s="67" t="str">
         <x:v>COLLECTION INPUT: tags[] → task_tags.tag (replace task tag set)</x:v>
@@ -8932,7 +8572,7 @@
         <x:v>tasks.id</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="15" hidden="0" customHeight="1">
+    <x:row r="142" ht="40" hidden="0" customHeight="1">
       <x:c r="A142" s="67" t="str">
         <x:v>API-TASK-006</x:v>
       </x:c>
@@ -8952,20 +8592,21 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G142" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>整数1..99</x:v>
       </x:c>
       <x:c r="H142" s="67" t="str">
-        <x:v>0..100</x:v>
+        <x:v>1..99</x:v>
       </x:c>
       <x:c r="I142" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J142" s="67" t="str">
-        <x:v>進捗率</x:v>
+        <x:v>IN_PROGRESSのみ更新可。100は確認依頼の状態変更で設定。</x:v>
       </x:c>
       <x:c r="K142" s="67" t="str">
         <x:v>tasks.progress</x:v>
       </x:c>
+      <x:c r="L142" s="241"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="67" t="str">
@@ -10072,7 +9713,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G174" s="67" t="str">
-        <x:v>最大50</x:v>
+        <x:v>最大100</x:v>
       </x:c>
       <x:c r="H174" s="67" t="str">
         <x:v>-</x:v>
@@ -10970,7 +10611,7 @@
         <x:v>Response</x:v>
       </x:c>
       <x:c r="C200" s="67" t="str">
-        <x:v>body</x:v>
+        <x:v>header</x:v>
       </x:c>
       <x:c r="D200" s="67" t="str">
         <x:v>response.header.Content-Type</x:v>
@@ -11005,7 +10646,7 @@
         <x:v>Response</x:v>
       </x:c>
       <x:c r="C201" s="67" t="str">
-        <x:v>body</x:v>
+        <x:v>header</x:v>
       </x:c>
       <x:c r="D201" s="67" t="str">
         <x:v>response.header.Content-Disposition</x:v>
@@ -11137,7 +10778,7 @@
         <x:v>task_attachments.id</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="15" hidden="0" customHeight="1">
+    <x:row r="205" ht="65" hidden="0" customHeight="1">
       <x:c r="A205" s="67" t="str">
         <x:v>API-TASK-011</x:v>
       </x:c>
@@ -11154,22 +10795,22 @@
         <x:v>Integer</x:v>
       </x:c>
       <x:c r="F205" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G205" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>0以上の整数</x:v>
       </x:c>
       <x:c r="H205" s="67" t="str">
         <x:v>int32</x:v>
       </x:c>
       <x:c r="I205" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J205" s="67" t="str">
-        <x:v>楽観Lock Version</x:v>
+        <x:v>Version。欠落/Null/形式不正=COMMON-4000、既存対象の不一致=COMMON-4090、削除済/不存在=COMMON-4040。権限確認後に判定。</x:v>
       </x:c>
       <x:c r="K205" s="67" t="str">
-        <x:v>tasks.version</x:v>
+        <x:v>task_attachments.version</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -11186,10 +10827,10 @@
         <x:v>response.body</x:v>
       </x:c>
       <x:c r="E206" s="67" t="str">
-        <x:v>Null</x:v>
+        <x:v>Bodyなし</x:v>
       </x:c>
       <x:c r="F206" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G206" s="67" t="str">
         <x:v>-</x:v>
@@ -11198,10 +10839,10 @@
         <x:v>No Content</x:v>
       </x:c>
       <x:c r="I206" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>該当なし</x:v>
       </x:c>
       <x:c r="J206" s="67" t="str">
-        <x:v>Response Bodyなし</x:v>
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K206" s="67" t="str">
         <x:v>-</x:v>
@@ -11221,9 +10862,7 @@
       <x:c r="K207" s="203"/>
     </x:row>
     <x:row r="208">
-      <x:c r="A208" s="186" t="str">
-        <x:v>JSON Path、型、必須、桁、Enum、Null、DB／生成元を外部契約として固定する。Path IDはDB型BIGINTに合わせLongとする。</x:v>
-      </x:c>
+      <x:c r="A208" s="186" t="str"/>
       <x:c r="B208" s="186"/>
       <x:c r="C208" s="186"/>
       <x:c r="D208" s="186"/>
@@ -11259,14 +10898,14 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="82" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
@@ -11300,8 +10939,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="247" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-13-SAMPLE</x:v>
@@ -11313,18 +10952,29 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="203" t="str">
+        <x:v>参考資料。Contract正本は23_API項目定義。Request例は送信区分別の表示用Object（そのまま送るJSONではない）。認証等の共通Headerは10／19参照。Binary PartはFile名で表記。各行は独立した例。</x:v>
+      </x:c>
+      <x:c r="B5" s="203"/>
+      <x:c r="C5" s="203"/>
+      <x:c r="D5" s="203"/>
+      <x:c r="E5" s="203"/>
+      <x:c r="F5" s="203"/>
+      <x:c r="G5" s="203"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -11360,7 +11010,7 @@
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="120" customHeight="1">
+    <x:row r="8" ht="115" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-TASK-001</x:v>
       </x:c>
@@ -11368,56 +11018,10 @@
         <x:v>Task検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>{
-  "query": {
-    "taskCode": "sample",
-    "title": "sample",
-    "projectId": 1001,
-    "assigneeId": 1001,
-    "reporterId": 1001,
-    "status": "TODO",
-    "priority": "LOW",
-    "dueFrom": "2026-08-10",
-    "dueTo": "2026-08-10",
-    "overdue": true,
-    "mine": true,
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"taskCode": "sample", "title": "sample", "projectId": 1001, "assigneeId": 1001, "reporterId": 1001, "status": ["TODO"], "priority": ["LOW"], "dueFrom": "2026-08-10", "dueTo": "2026-08-10", "overdue": false, "mine": true, "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "taskCode": "sample",
-        "projectId": 1001,
-        "projectName": "サンプル",
-        "title": "sample",
-        "assigneeId": 1001,
-        "assigneeName": "サンプル",
-        "status": "TODO",
-        "priority": "LOW",
-        "dueDate": "2026-08-10",
-        "progress": 50,
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "taskCode": "sample", "projectId": 1001, "projectName": "サンプル", "title": "sample", "assigneeId": 1001, "assigneeName": "サンプル", "status": "TODO", "priority": "LOW", "dueDate": "2026-08-10", "progress": 0, "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>200</x:v>
@@ -11429,7 +11033,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="120" customHeight="1">
+    <x:row r="9" ht="190" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-TASK-002</x:v>
       </x:c>
@@ -11437,70 +11041,10 @@
         <x:v>Task詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "taskCode": "sample",
-    "projectId": 1001,
-    "projectName": "サンプル",
-    "title": "sample",
-    "assigneeId": 1001,
-    "assigneeName": "サンプル",
-    "status": "TODO",
-    "priority": "LOW",
-    "dueDate": "2026-08-10",
-    "progress": 50,
-    "version": 1,
-    "description": "sample",
-    "reporterId": 1001,
-    "startDate": "2026-08-10",
-    "estimatedHours": 7.5,
-    "tags": [
-      "SAMPLE"
-    ],
-    "comments": [
-      {
-        "id": 1001,
-        "comment": "sample",
-        "userId": 1001,
-        "userName": "サンプル",
-        "createdAt": "2026-08-10T10:00:00+09:00"
-      }
-    ],
-    "attachments": [
-      {
-        "id": 1001,
-        "originalName": "サンプル",
-        "fileSize": 1001,
-        "mimeType": "sample",
-        "createdBy": 1001,
-        "createdAt": "2026-08-10T10:00:00+09:00",
-        "version": 1
-      }
-    ],
-    "histories": [
-      {
-        "id": 1001,
-        "fieldName": "サンプル",
-        "beforeValue": "sample",
-        "afterValue": "sample",
-        "changedBy": 1001,
-        "changedAt": "2026-08-10T10:00:00+09:00"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "taskCode": "sample", "projectId": 1001, "projectName": "サンプル", "title": "sample", "assigneeId": 1001, "assigneeName": "サンプル", "status": "TODO", "priority": "LOW", "dueDate": "2026-08-10", "progress": 0, "version": 1, "description": "sample", "reporterId": 1001, "startDate": "2026-08-10", "estimatedHours": 7.5, "tags": ["SAMPLE"], "comments": [{"id": 1001, "comment": "sample", "userId": 1001, "userName": "サンプル", "createdAt": "2026-08-10T10:00:00+09:00"}], "attachments": [{"id": 1001, "originalName": "sample.pdf", "fileSize": 1001, "mimeType": "application/pdf", "createdBy": 1001, "createdAt": "2026-08-10T10:00:00+09:00", "version": 1}], "histories": [{"id": 1001, "fieldName": "サンプル", "beforeValue": "sample", "afterValue": "sample", "changedBy": 1001, "changedAt": "2026-08-10T10:00:00+09:00"}]}}</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>200</x:v>
@@ -11512,7 +11056,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="120" customHeight="1">
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-TASK-003</x:v>
       </x:c>
@@ -11520,40 +11064,10 @@
         <x:v>Task登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>{
-  "body": {
-    "projectId": 1001,
-    "title": "sample",
-    "description": "sample",
-    "assigneeId": 1001,
-    "priority": "LOW",
-    "startDate": "2026-08-10",
-    "dueDate": "2026-08-10",
-    "estimatedHours": 7.5,
-    "parentTaskId": 1001,
-    "tags": [
-      "SAMPLE"
-    ]
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"projectId": 1001, "title": "sample", "description": "sample", "assigneeId": 1001, "priority": "LOW", "startDate": "2026-08-10", "dueDate": "2026-08-10", "estimatedHours": 7.5, "parentTaskId": null, "tags": ["SAMPLE"]}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "taskCode": "sample",
-    "status": "TODO",
-    "progress": 50,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "taskCode": "sample", "status": "TODO", "progress": 0, "version": 0}}</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>201</x:v>
@@ -11565,7 +11079,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="120" customHeight="1">
+    <x:row r="11" ht="100" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-TASK-004</x:v>
       </x:c>
@@ -11573,37 +11087,10 @@
         <x:v>Task更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "title": "sample",
-    "description": "sample",
-    "assigneeId": 1001,
-    "priority": "LOW",
-    "startDate": "2026-08-10",
-    "dueDate": "2026-08-10",
-    "estimatedHours": 7.5,
-    "parentTaskId": 1001,
-    "tags": [
-      "SAMPLE"
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"title": "sample", "description": "sample", "assigneeId": 1001, "priority": "LOW", "startDate": "2026-08-10", "dueDate": "2026-08-10", "estimatedHours": 7.5, "parentTaskId": null, "tags": ["SAMPLE"], "version": 1}}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 2}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
@@ -11615,7 +11102,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="120" customHeight="1">
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-TASK-005</x:v>
       </x:c>
@@ -11623,29 +11110,10 @@
         <x:v>Task状態更新</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "targetStatus": "IN_PROGRESS",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"targetStatus": "IN_PROGRESS", "version": 1}}</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "previousStatus": "sample",
-    "currentStatus": "sample",
-    "progress": 50,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"previousStatus": "TODO", "currentStatus": "IN_PROGRESS", "progress": 1, "version": 2}}</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>200</x:v>
@@ -11654,10 +11122,10 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="120" customHeight="1">
+        <x:v>例の前提：PJ=IN_PROGRESS、Task=TODO、version=1。着手成功。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="100" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-TASK-006</x:v>
       </x:c>
@@ -11665,28 +11133,10 @@
         <x:v>進捗更新</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "progress": 50,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"progress": 50, "version": 1}}</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "progress": 50,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "progress": 50, "version": 2}}</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>200</x:v>
@@ -11695,10 +11145,10 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="120" customHeight="1">
+        <x:v>例の前提：PJ/TaskともにIN_PROGRESS、version=1。進捗のみ変更。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-TASK-007</x:v>
       </x:c>
@@ -11706,31 +11156,10 @@
         <x:v>Comment登録</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "comment": "sample"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"comment": "sample"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "comment": "sample",
-    "user": "sample",
-    "createdAt": "2026-08-10T10:00:00+09:00"
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "comment": "sample", "user": "sample", "createdAt": "2026-08-10T10:00:00+09:00"}}</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>201</x:v>
@@ -11742,7 +11171,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="120" customHeight="1">
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-TASK-008</x:v>
       </x:c>
@@ -11750,41 +11179,10 @@
         <x:v>履歴検索</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "query": {
-    "page": 0,
-    "size": 20
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "query": {"page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "fieldName": "サンプル",
-        "beforeValue": "sample",
-        "afterValue": "sample",
-        "changedBy": 1001,
-        "changedAt": "2026-08-10T10:00:00+09:00"
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "fieldName": "サンプル", "beforeValue": "sample", "afterValue": "sample", "changedBy": 1001, "changedAt": "2026-08-10T10:00:00+09:00"}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>200</x:v>
@@ -11796,7 +11194,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="120" customHeight="1">
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-TASK-009</x:v>
       </x:c>
@@ -11804,32 +11202,10 @@
         <x:v>添付登録</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>{
-  "multipart": {
-    "file": "sample"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  },
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"multipart": {"file": "sample.pdf（Binary Part）"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}, "path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-12T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "originalName": "sample.pdf",
-    "fileSize": 102400,
-    "mimeType": "application/pdf",
-    "createdAt": "2026-08-12T10:00:00+09:00"
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-12T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "originalName": "sample.pdf", "fileSize": 102400, "mimeType": "application/pdf", "createdAt": "2026-08-12T10:00:00+09:00"}}</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>201</x:v>
@@ -11841,7 +11217,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="120" customHeight="1">
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-TASK-010</x:v>
       </x:c>
@@ -11849,12 +11225,7 @@
         <x:v>添付取得</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001,
-    "attachmentId": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001, "attachmentId": 1001}}</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
         <x:v>&lt;binary stream&gt;</x:v>
@@ -11863,13 +11234,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>binary</x:v>
+        <x:v>application/pdf</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。Content-Disposition: attachment; filename="sample.pdf"; filename*=UTF-8''sample.pdf。BodyはBinary。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="100" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-TASK-011</x:v>
       </x:c>
@@ -11877,15 +11248,7 @@
         <x:v>添付削除</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001,
-    "attachmentId": 1001
-  },
-  "query": {
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001, "attachmentId": 1001}, "query": {"version": 1}}</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -11928,344 +11291,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="138" t="str">
-        <x:v>API権限対応</x:v>
-      </x:c>
-      <x:c r="B1" s="138"/>
-      <x:c r="C1" s="138"/>
-      <x:c r="D1" s="138"/>
-      <x:c r="E1" s="138"/>
-      <x:c r="F1" s="138"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="138"/>
-      <x:c r="B2" s="138"/>
-      <x:c r="C2" s="138"/>
-      <x:c r="D2" s="138"/>
-      <x:c r="E2" s="138"/>
-      <x:c r="F2" s="138"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="141" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="141" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="139" t="str">
-        <x:v>CW-BD-13-PERM</x:v>
-      </x:c>
-      <x:c r="E3" s="139"/>
-      <x:c r="F3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="141" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="141" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="E4" s="139"/>
-      <x:c r="F4" s="139"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="142" t="str">
-        <x:v>1. API・Permission・Data範囲</x:v>
-      </x:c>
-      <x:c r="B6" s="142"/>
-      <x:c r="C6" s="142"/>
-      <x:c r="D6" s="142"/>
-      <x:c r="E6" s="142"/>
-      <x:c r="F6" s="142"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="147" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:v>API名</x:v>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:v>Permission Code</x:v>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:v>許可Role</x:v>
-      </x:c>
-      <x:c r="E7" s="147" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="147" t="str">
-        <x:v>判定方式</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="151" t="str">
-        <x:v>API-TASK-001</x:v>
-      </x:c>
-      <x:c r="B8" s="151" t="str">
-        <x:v>Task検索</x:v>
-      </x:c>
-      <x:c r="C8" s="151" t="str">
-        <x:v>PERM-TASK-READ</x:v>
-      </x:c>
-      <x:c r="D8" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E8" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=参加PJ・本人Task</x:v>
-      </x:c>
-      <x:c r="F8" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="151" t="str">
-        <x:v>API-TASK-002</x:v>
-      </x:c>
-      <x:c r="B9" s="151" t="str">
-        <x:v>Task詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="151" t="str">
-        <x:v>PERM-TASK-READ</x:v>
-      </x:c>
-      <x:c r="D9" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E9" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F9" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="151" t="str">
-        <x:v>API-TASK-003</x:v>
-      </x:c>
-      <x:c r="B10" s="151" t="str">
-        <x:v>Task登録</x:v>
-      </x:c>
-      <x:c r="C10" s="151" t="str">
-        <x:v>PERM-TASK-WRITE</x:v>
-      </x:c>
-      <x:c r="D10" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E10" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="F10" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="151" t="str">
-        <x:v>API-TASK-004</x:v>
-      </x:c>
-      <x:c r="B11" s="151" t="str">
-        <x:v>Task更新</x:v>
-      </x:c>
-      <x:c r="C11" s="151" t="str">
-        <x:v>PERM-TASK-WRITE</x:v>
-      </x:c>
-      <x:c r="D11" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E11" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="F11" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="151" t="str">
-        <x:v>API-TASK-005</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="str">
-        <x:v>Task状態更新</x:v>
-      </x:c>
-      <x:c r="C12" s="151" t="str">
-        <x:v>PERM-TASK-WRITE / PERM-TASK-PROGRESS / PERM-TASK-APPROVE</x:v>
-      </x:c>
-      <x:c r="D12" s="151" t="str">
-        <x:v>権限別</x:v>
-      </x:c>
-      <x:c r="E12" s="151" t="str">
-        <x:v>担当者=TODO/進行/REVIEW; PM/ADMIN=承認・差戻し・取消</x:v>
-      </x:c>
-      <x:c r="F12" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="151" t="str">
-        <x:v>API-TASK-006</x:v>
-      </x:c>
-      <x:c r="B13" s="151" t="str">
-        <x:v>進捗更新</x:v>
-      </x:c>
-      <x:c r="C13" s="151" t="str">
-        <x:v>PERM-TASK-PROGRESS</x:v>
-      </x:c>
-      <x:c r="D13" s="151" t="str">
-        <x:v>担当者/PM/管理者</x:v>
-      </x:c>
-      <x:c r="E13" s="151" t="str">
-        <x:v>担当者または担当PM/ADMIN</x:v>
-      </x:c>
-      <x:c r="F13" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-PROGRESS') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="151" t="str">
-        <x:v>API-TASK-007</x:v>
-      </x:c>
-      <x:c r="B14" s="151" t="str">
-        <x:v>Comment登録</x:v>
-      </x:c>
-      <x:c r="C14" s="151" t="str">
-        <x:v>PERM-TASK-READ（PJ Member）</x:v>
-      </x:c>
-      <x:c r="D14" s="151" t="str">
-        <x:v>PJ Member</x:v>
-      </x:c>
-      <x:c r="E14" s="151" t="str">
-        <x:v>当該PJ Member</x:v>
-      </x:c>
-      <x:c r="F14" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-READ（PJ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="151" t="str">
-        <x:v>API-TASK-008</x:v>
-      </x:c>
-      <x:c r="B15" s="151" t="str">
-        <x:v>履歴検索</x:v>
-      </x:c>
-      <x:c r="C15" s="151" t="str">
-        <x:v>PERM-TASK-READ</x:v>
-      </x:c>
-      <x:c r="D15" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E15" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F15" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="151" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B16" s="151" t="str">
-        <x:v>添付登録</x:v>
-      </x:c>
-      <x:c r="C16" s="151" t="str">
-        <x:v>PERM-FILE-WRITE</x:v>
-      </x:c>
-      <x:c r="D16" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E16" s="151" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
-      </x:c>
-      <x:c r="F16" s="151" t="str">
-        <x:v>hasAuthority('PERM-FILE-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="151" t="str">
-        <x:v>API-TASK-010</x:v>
-      </x:c>
-      <x:c r="B17" s="151" t="str">
-        <x:v>添付取得</x:v>
-      </x:c>
-      <x:c r="C17" s="151" t="str">
-        <x:v>PERM-TASK-READ</x:v>
-      </x:c>
-      <x:c r="D17" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E17" s="151" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
-      </x:c>
-      <x:c r="F17" s="151" t="str">
-        <x:v>hasAuthority('PERM-TASK-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="151" t="str">
-        <x:v>API-TASK-011</x:v>
-      </x:c>
-      <x:c r="B18" s="151" t="str">
-        <x:v>添付削除</x:v>
-      </x:c>
-      <x:c r="C18" s="151" t="str">
-        <x:v>PERM-FILE-WRITE</x:v>
-      </x:c>
-      <x:c r="D18" s="151" t="str">
-        <x:v>権限者</x:v>
-      </x:c>
-      <x:c r="E18" s="151" t="str">
-        <x:v>ADMIN/担当PM/Upload者</x:v>
-      </x:c>
-      <x:c r="F18" s="151" t="str">
-        <x:v>hasAuthority('PERM-FILE-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="155" t="str">
-        <x:v>ControllerのRole表示だけで認可しない。Service層でPermission Code、本人/PJ Member/担当PM等のData範囲、対象Dataの存在を再判定する。</x:v>
-      </x:c>
-      <x:c r="B20" s="155"/>
-      <x:c r="C20" s="155"/>
-      <x:c r="D20" s="155"/>
-      <x:c r="E20" s="155"/>
-      <x:c r="F20" s="155"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="155"/>
-      <x:c r="B21" s="155"/>
-      <x:c r="C21" s="155"/>
-      <x:c r="D21" s="155"/>
-      <x:c r="E21" s="155"/>
-      <x:c r="F21" s="155"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A20:F21"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>